--- a/ejemplos/03-predictivo/simulador/base_datos_simulada.xlsx
+++ b/ejemplos/03-predictivo/simulador/base_datos_simulada.xlsx
@@ -347,7 +347,7 @@
     <t>Versión</t>
   </si>
   <si>
-    <t>2027.01.01</t>
+    <t>2027.01.03</t>
   </si>
   <si>
     <t>Generada</t>

--- a/ejemplos/03-predictivo/simulador/base_datos_simulada.xlsx
+++ b/ejemplos/03-predictivo/simulador/base_datos_simulada.xlsx
@@ -347,7 +347,7 @@
     <t>Versión</t>
   </si>
   <si>
-    <t>2027.01.03</t>
+    <t>2027.01.15</t>
   </si>
   <si>
     <t>Generada</t>

--- a/ejemplos/03-predictivo/simulador/base_datos_simulada.xlsx
+++ b/ejemplos/03-predictivo/simulador/base_datos_simulada.xlsx
@@ -347,7 +347,7 @@
     <t>Versión</t>
   </si>
   <si>
-    <t>2027.01.15</t>
+    <t>2027.01.16</t>
   </si>
   <si>
     <t>Generada</t>
